--- a/apps/api/assets/vocabulary/小学/人教版/六年级上.xlsx
+++ b/apps/api/assets/vocabulary/小学/人教版/六年级上.xlsx
@@ -440,7 +440,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D148"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -1064,6 +1064,16 @@
           <t>on foot</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 步行；在进行中；徒步
@@ -1299,6 +1309,16 @@
           <t>slow down</t>
         </is>
       </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 闲下来；减缓；放慢速度；减速
@@ -1474,6 +1494,16 @@
           <t>pay attention to</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 注意
@@ -1509,6 +1539,16 @@
       <c r="A47" s="2" t="inlineStr">
         <is>
           <t>traffic lights</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -1665,6 +1705,16 @@
           <t>Papa Westray</t>
         </is>
       </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
           <t>帕帕威斯垂岛</t>
@@ -1747,6 +1797,16 @@
           <t>see a film</t>
         </is>
       </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 看电影；去看电影；去电影院看电影</t>
@@ -1784,6 +1844,16 @@
           <t>take a trip</t>
         </is>
       </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 旅行
@@ -1957,6 +2027,16 @@
           <t>comic book</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 漫画书
@@ -2157,6 +2237,16 @@
           <t>Mid-Autumn Festival</t>
         </is>
       </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
           <t>《英汉医学词典》mid autumn festival
@@ -2191,6 +2281,16 @@
       <c r="A79" s="2" t="inlineStr">
         <is>
           <t>get together</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -2831,6 +2931,16 @@
           <t>head teacher</t>
         </is>
       </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 校长
@@ -3182,6 +3292,16 @@
       <c r="A123" s="2" t="inlineStr">
         <is>
           <t>see a doctor</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -3293,6 +3413,16 @@
           <t>take a deep breath</t>
         </is>
       </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 行深呼吸
